--- a/assets/Temporary_Blocking.xlsx
+++ b/assets/Temporary_Blocking.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://earthboundtradingcom-my.sharepoint.com/personal/wesley_earthboundtrading_com/Documents/Desktop/EBT_AI_Project/Tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wesley\Documents\WebOrderAI\weborder-ai\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{6D8E9985-D060-4357-BE57-E22F78CB3C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7381E456-9ECF-4048-90D1-8CFE9805DB1E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E5C9D9-E82D-42AC-9EC1-BD6E653C3CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5AB706BD-6508-4EDB-A813-24A3FE7B8A23}"/>
   </bookViews>
